--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0003T0006Z000C1N13_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0003T0006Z000C1N13_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>17.0954574759716</v>
+        <v>2.778011839845385</v>
       </c>
       <c r="D2" t="n">
-        <v>14.95662712863519</v>
+        <v>2.430451908403219</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
